--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,2716 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121719893</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>416196</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7038951</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121719881</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>416016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7039217</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121719945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74722</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>416110</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121719938</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95361</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2420</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogstimmia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Timmia austriaca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416137</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039127</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121719877</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79663</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>416081</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039208</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121719885</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>416095</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039081</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121719888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>77553</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>416207</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039007</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121719942</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig knopplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Biatora fallax</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>416016</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039216</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121719937</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416161</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039079</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121719894</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79601</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>416218</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7038922</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121719878</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79742</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>416081</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039209</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121719884</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57357</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>416043</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7039154</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121719890</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79698</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>416194</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7038973</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121719940</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95361</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2420</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogstimmia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Timmia austriaca</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>416053</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039233</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121719941</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82400</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>416015</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039205</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121719880</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79663</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>416016</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039217</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121719892</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74722</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>416199</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7038968</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121719891</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77553</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>416194</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7038972</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121719887</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80651</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229558</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Barkporlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pertusaria sommerfeltii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Flörke ex Sommerf.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>416179</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7039023</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121719948</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79601</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>416217</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7038926</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121719950</v>
+      </c>
+      <c r="B23" t="n">
+        <v>94614</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>416218</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7038929</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121719879</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79698</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>416015</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7039216</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121719939</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79698</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>416083</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7039207</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121719933</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80284</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>738</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>416132</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7039143</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121719889</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79601</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>416197</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7038994</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121719882</v>
+      </c>
+      <c r="B28" t="n">
+        <v>74713</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>492</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>416035</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7039188</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719940</v>
+        <v>121719941</v>
       </c>
       <c r="B3" t="n">
-        <v>95361</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2420</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416053</v>
+        <v>416015</v>
       </c>
       <c r="R3" t="n">
-        <v>7039233</v>
+        <v>7039205</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719878</v>
+        <v>121719945</v>
       </c>
       <c r="B4" t="n">
-        <v>79742</v>
+        <v>74722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229504</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416081</v>
+        <v>416110</v>
       </c>
       <c r="R4" t="n">
-        <v>7039209</v>
+        <v>7039093</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719880</v>
+        <v>121719878</v>
       </c>
       <c r="B5" t="n">
-        <v>79663</v>
+        <v>79742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229748</v>
+        <v>229504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R5" t="n">
-        <v>7039217</v>
+        <v>7039209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,11 +1094,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719882</v>
+        <v>121719885</v>
       </c>
       <c r="B6" t="n">
-        <v>74713</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416035</v>
+        <v>416095</v>
       </c>
       <c r="R6" t="n">
-        <v>7039188</v>
+        <v>7039081</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,11 +1196,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1222,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719877</v>
+        <v>121719940</v>
       </c>
       <c r="B7" t="n">
-        <v>79663</v>
+        <v>95361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>2420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416081</v>
+        <v>416053</v>
       </c>
       <c r="R7" t="n">
-        <v>7039208</v>
+        <v>7039233</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,12 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,31 +1298,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719889</v>
+        <v>121719933</v>
       </c>
       <c r="B8" t="n">
-        <v>79601</v>
+        <v>80284</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,44 +1326,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>738</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416197</v>
+        <v>416132</v>
       </c>
       <c r="R8" t="n">
-        <v>7038994</v>
+        <v>7039143</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,12 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,29 +1398,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719938</v>
+        <v>121719948</v>
       </c>
       <c r="B9" t="n">
-        <v>95361</v>
+        <v>79601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1432,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2420</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416137</v>
+        <v>416217</v>
       </c>
       <c r="R9" t="n">
-        <v>7039127</v>
+        <v>7038926</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1537,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719892</v>
+        <v>121719889</v>
       </c>
       <c r="B10" t="n">
-        <v>74722</v>
+        <v>79601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,38 +1530,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416199</v>
+        <v>416197</v>
       </c>
       <c r="R10" t="n">
-        <v>7038968</v>
+        <v>7038994</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,6 +1605,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719942</v>
+        <v>121719884</v>
       </c>
       <c r="B11" t="n">
-        <v>79048</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,41 +1636,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1778</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416016</v>
+        <v>416043</v>
       </c>
       <c r="R11" t="n">
-        <v>7039216</v>
+        <v>7039154</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,12 +1699,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719885</v>
+        <v>121719879</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416095</v>
+        <v>416015</v>
       </c>
       <c r="R12" t="n">
-        <v>7039081</v>
+        <v>7039216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,6 +1822,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719888</v>
+        <v>121719937</v>
       </c>
       <c r="B13" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416207</v>
+        <v>416161</v>
       </c>
       <c r="R13" t="n">
-        <v>7039007</v>
+        <v>7039079</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,31 +1929,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719941</v>
+        <v>121719950</v>
       </c>
       <c r="B14" t="n">
-        <v>82400</v>
+        <v>94614</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416015</v>
+        <v>416218</v>
       </c>
       <c r="R14" t="n">
-        <v>7039205</v>
+        <v>7038929</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2052,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719879</v>
+        <v>121719877</v>
       </c>
       <c r="B15" t="n">
-        <v>79698</v>
+        <v>79663</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416015</v>
+        <v>416081</v>
       </c>
       <c r="R15" t="n">
-        <v>7039216</v>
+        <v>7039208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2159,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719948</v>
+        <v>121719942</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>79048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1778</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416217</v>
+        <v>416016</v>
       </c>
       <c r="R16" t="n">
-        <v>7038926</v>
+        <v>7039216</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2261,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719881</v>
+        <v>121719890</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416016</v>
+        <v>416194</v>
       </c>
       <c r="R17" t="n">
-        <v>7039217</v>
+        <v>7038973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2345,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2368,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719894</v>
+        <v>121719881</v>
       </c>
       <c r="B18" t="n">
-        <v>79601</v>
+        <v>79726</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416218</v>
+        <v>416016</v>
       </c>
       <c r="R18" t="n">
-        <v>7038922</v>
+        <v>7039217</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2449,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719939</v>
+        <v>121719893</v>
       </c>
       <c r="B19" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,21 +2486,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416083</v>
+        <v>416196</v>
       </c>
       <c r="R19" t="n">
-        <v>7039207</v>
+        <v>7038951</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2560,22 +2560,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719933</v>
+        <v>121719887</v>
       </c>
       <c r="B20" t="n">
-        <v>80284</v>
+        <v>80651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,41 +2584,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>738</v>
+        <v>229558</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416132</v>
+        <v>416179</v>
       </c>
       <c r="R20" t="n">
-        <v>7039143</v>
+        <v>7039023</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2642,12 +2645,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2656,28 +2659,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719884</v>
+        <v>121719882</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>74713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,43 +2690,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416043</v>
+        <v>416035</v>
       </c>
       <c r="R21" t="n">
-        <v>7039154</v>
+        <v>7039188</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,11 +2756,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2770,6 +2764,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2786,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719887</v>
+        <v>121719888</v>
       </c>
       <c r="B22" t="n">
-        <v>80651</v>
+        <v>77553</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,37 +2801,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229558</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416179</v>
+        <v>416207</v>
       </c>
       <c r="R22" t="n">
-        <v>7039023</v>
+        <v>7039007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,9 +2869,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719891</v>
+        <v>121719894</v>
       </c>
       <c r="B23" t="n">
-        <v>77553</v>
+        <v>79601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,25 +2904,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416194</v>
+        <v>416218</v>
       </c>
       <c r="R23" t="n">
-        <v>7038972</v>
+        <v>7038922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,11 +2978,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719893</v>
+        <v>121719880</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>79663</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,25 +3006,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416196</v>
+        <v>416016</v>
       </c>
       <c r="R24" t="n">
-        <v>7038951</v>
+        <v>7039217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,6 +3080,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3101,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719950</v>
+        <v>121719891</v>
       </c>
       <c r="B25" t="n">
-        <v>94614</v>
+        <v>77553</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,25 +3113,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416218</v>
+        <v>416194</v>
       </c>
       <c r="R25" t="n">
-        <v>7038929</v>
+        <v>7038972</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3187,26 +3187,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719937</v>
+        <v>121719892</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,13 +3248,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416161</v>
+        <v>416199</v>
       </c>
       <c r="R26" t="n">
-        <v>7039079</v>
+        <v>7038968</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3273,12 +3278,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3293,19 +3298,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719890</v>
+        <v>121719939</v>
       </c>
       <c r="B27" t="n">
         <v>79698</v>
@@ -3345,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416194</v>
+        <v>416083</v>
       </c>
       <c r="R27" t="n">
-        <v>7038973</v>
+        <v>7039207</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3375,12 +3380,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,31 +3396,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719945</v>
+        <v>121719938</v>
       </c>
       <c r="B28" t="n">
-        <v>74722</v>
+        <v>95361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>2420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416110</v>
+        <v>416137</v>
       </c>
       <c r="R28" t="n">
-        <v>7039093</v>
+        <v>7039127</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719941</v>
+        <v>121719933</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>80284</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>738</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416015</v>
+        <v>416132</v>
       </c>
       <c r="R3" t="n">
-        <v>7039205</v>
+        <v>7039143</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719945</v>
+        <v>121719940</v>
       </c>
       <c r="B4" t="n">
-        <v>74722</v>
+        <v>95361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>2420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416110</v>
+        <v>416053</v>
       </c>
       <c r="R4" t="n">
-        <v>7039093</v>
+        <v>7039233</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719878</v>
+        <v>121719889</v>
       </c>
       <c r="B5" t="n">
-        <v>79742</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1020,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229504</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416081</v>
+        <v>416197</v>
       </c>
       <c r="R5" t="n">
-        <v>7039209</v>
+        <v>7038994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1095,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719885</v>
+        <v>121719888</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>77553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416095</v>
+        <v>416207</v>
       </c>
       <c r="R6" t="n">
-        <v>7039081</v>
+        <v>7039007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1200,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1212,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719940</v>
+        <v>121719884</v>
       </c>
       <c r="B7" t="n">
-        <v>95361</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,41 +1233,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2420</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416053</v>
+        <v>416043</v>
       </c>
       <c r="R7" t="n">
-        <v>7039233</v>
+        <v>7039154</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1296,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,22 +1321,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719933</v>
+        <v>121719877</v>
       </c>
       <c r="B8" t="n">
-        <v>80284</v>
+        <v>79663</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>738</v>
+        <v>229748</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1373,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416132</v>
+        <v>416081</v>
       </c>
       <c r="R8" t="n">
-        <v>7039143</v>
+        <v>7039208</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,12 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,26 +1419,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719948</v>
+        <v>121719887</v>
       </c>
       <c r="B9" t="n">
-        <v>79601</v>
+        <v>80651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,41 +1452,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>229558</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416217</v>
+        <v>416179</v>
       </c>
       <c r="R9" t="n">
-        <v>7038926</v>
+        <v>7039023</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,12 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,28 +1527,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719889</v>
+        <v>121719885</v>
       </c>
       <c r="B10" t="n">
-        <v>79601</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,41 +1558,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416197</v>
+        <v>416095</v>
       </c>
       <c r="R10" t="n">
-        <v>7038994</v>
+        <v>7039081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,7 +1630,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719884</v>
+        <v>121719893</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416043</v>
+        <v>416196</v>
       </c>
       <c r="R11" t="n">
-        <v>7039154</v>
+        <v>7038951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719879</v>
+        <v>121719941</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1793,10 @@
         <v>416015</v>
       </c>
       <c r="R12" t="n">
-        <v>7039216</v>
+        <v>7039205</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,12 +1820,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,31 +1836,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719937</v>
+        <v>121719938</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>95361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1864,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416161</v>
+        <v>416137</v>
       </c>
       <c r="R13" t="n">
-        <v>7039079</v>
+        <v>7039127</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1945,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719950</v>
+        <v>121719948</v>
       </c>
       <c r="B14" t="n">
-        <v>94614</v>
+        <v>79601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416218</v>
+        <v>416217</v>
       </c>
       <c r="R14" t="n">
-        <v>7038929</v>
+        <v>7038926</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2047,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719877</v>
+        <v>121719939</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>79698</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2068,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,13 +2096,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416081</v>
+        <v>416083</v>
       </c>
       <c r="R15" t="n">
-        <v>7039208</v>
+        <v>7039207</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2117,12 +2126,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,31 +2142,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719942</v>
+        <v>121719894</v>
       </c>
       <c r="B16" t="n">
-        <v>79048</v>
+        <v>79601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1778</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,13 +2198,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416016</v>
+        <v>416218</v>
       </c>
       <c r="R16" t="n">
-        <v>7039216</v>
+        <v>7038922</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2224,12 +2228,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,22 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719890</v>
+        <v>121719892</v>
       </c>
       <c r="B17" t="n">
-        <v>79698</v>
+        <v>74722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416194</v>
+        <v>416199</v>
       </c>
       <c r="R17" t="n">
-        <v>7038973</v>
+        <v>7038968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,11 +2346,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2363,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719881</v>
+        <v>121719890</v>
       </c>
       <c r="B18" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,25 +2374,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416016</v>
+        <v>416194</v>
       </c>
       <c r="R18" t="n">
-        <v>7039217</v>
+        <v>7038973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2451,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2470,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719893</v>
+        <v>121719879</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416196</v>
+        <v>416015</v>
       </c>
       <c r="R19" t="n">
-        <v>7038951</v>
+        <v>7039216</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,6 +2555,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2572,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719887</v>
+        <v>121719937</v>
       </c>
       <c r="B20" t="n">
-        <v>80651</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,40 +2592,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416179</v>
+        <v>416161</v>
       </c>
       <c r="R20" t="n">
-        <v>7039023</v>
+        <v>7039079</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,12 +2646,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,29 +2660,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719882</v>
+        <v>121719950</v>
       </c>
       <c r="B21" t="n">
-        <v>74713</v>
+        <v>94614</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,25 +2690,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416035</v>
+        <v>416218</v>
       </c>
       <c r="R21" t="n">
-        <v>7039188</v>
+        <v>7038929</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2764,31 +2764,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719888</v>
+        <v>121719881</v>
       </c>
       <c r="B22" t="n">
-        <v>77553</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,25 +2792,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416207</v>
+        <v>416016</v>
       </c>
       <c r="R22" t="n">
-        <v>7039007</v>
+        <v>7039217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,7 +2869,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
+          <t>en</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2892,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719894</v>
+        <v>121719880</v>
       </c>
       <c r="B23" t="n">
-        <v>79601</v>
+        <v>79663</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>229748</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416218</v>
+        <v>416016</v>
       </c>
       <c r="R23" t="n">
-        <v>7038922</v>
+        <v>7039217</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,6 +2973,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719880</v>
+        <v>121719891</v>
       </c>
       <c r="B24" t="n">
-        <v>79663</v>
+        <v>77553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,25 +3006,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416016</v>
+        <v>416194</v>
       </c>
       <c r="R24" t="n">
-        <v>7039217</v>
+        <v>7038972</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719891</v>
+        <v>121719878</v>
       </c>
       <c r="B25" t="n">
-        <v>77553</v>
+        <v>79742</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>229504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416194</v>
+        <v>416081</v>
       </c>
       <c r="R25" t="n">
-        <v>7038972</v>
+        <v>7039209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3187,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3208,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719892</v>
+        <v>121719882</v>
       </c>
       <c r="B26" t="n">
-        <v>74722</v>
+        <v>74713</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3215,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416199</v>
+        <v>416035</v>
       </c>
       <c r="R26" t="n">
-        <v>7038968</v>
+        <v>7039188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3289,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719939</v>
+        <v>121719945</v>
       </c>
       <c r="B27" t="n">
-        <v>79698</v>
+        <v>74722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416083</v>
+        <v>416110</v>
       </c>
       <c r="R27" t="n">
-        <v>7039207</v>
+        <v>7039093</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719938</v>
+        <v>121719942</v>
       </c>
       <c r="B28" t="n">
-        <v>95361</v>
+        <v>79048</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2420</v>
+        <v>1778</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416137</v>
+        <v>416016</v>
       </c>
       <c r="R28" t="n">
-        <v>7039127</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719892</v>
+        <v>121719890</v>
       </c>
       <c r="B17" t="n">
-        <v>74722</v>
+        <v>79698</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416199</v>
+        <v>416194</v>
       </c>
       <c r="R17" t="n">
-        <v>7038968</v>
+        <v>7038973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2346,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2362,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719890</v>
+        <v>121719892</v>
       </c>
       <c r="B18" t="n">
-        <v>79698</v>
+        <v>74722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416194</v>
+        <v>416199</v>
       </c>
       <c r="R18" t="n">
-        <v>7038973</v>
+        <v>7038968</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,11 +2453,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719891</v>
+        <v>121719945</v>
       </c>
       <c r="B24" t="n">
-        <v>77553</v>
+        <v>74722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416194</v>
+        <v>416110</v>
       </c>
       <c r="R24" t="n">
-        <v>7038972</v>
+        <v>7039093</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,31 +3080,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719878</v>
+        <v>121719882</v>
       </c>
       <c r="B25" t="n">
-        <v>79742</v>
+        <v>74713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,25 +3108,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229504</v>
+        <v>492</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416081</v>
+        <v>416035</v>
       </c>
       <c r="R25" t="n">
-        <v>7039209</v>
+        <v>7039188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3182,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719882</v>
+        <v>121719878</v>
       </c>
       <c r="B26" t="n">
-        <v>74713</v>
+        <v>79742</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>229504</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416035</v>
+        <v>416081</v>
       </c>
       <c r="R26" t="n">
-        <v>7039188</v>
+        <v>7039209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,11 +3289,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719945</v>
+        <v>121719891</v>
       </c>
       <c r="B27" t="n">
-        <v>74722</v>
+        <v>77553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,21 +3321,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3345,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416110</v>
+        <v>416194</v>
       </c>
       <c r="R27" t="n">
-        <v>7039093</v>
+        <v>7038972</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3380,12 +3375,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,16 +3391,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719933</v>
+        <v>121719938</v>
       </c>
       <c r="B3" t="n">
-        <v>80284</v>
+        <v>95361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>738</v>
+        <v>2420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416132</v>
+        <v>416137</v>
       </c>
       <c r="R3" t="n">
-        <v>7039143</v>
+        <v>7039127</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719940</v>
+        <v>121719893</v>
       </c>
       <c r="B4" t="n">
-        <v>95361</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416053</v>
+        <v>416196</v>
       </c>
       <c r="R4" t="n">
-        <v>7039233</v>
+        <v>7038951</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719889</v>
+        <v>121719884</v>
       </c>
       <c r="B5" t="n">
-        <v>79601</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1020,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416197</v>
+        <v>416043</v>
       </c>
       <c r="R5" t="n">
-        <v>7038994</v>
+        <v>7039154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,13 +1091,17 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719888</v>
+        <v>121719889</v>
       </c>
       <c r="B6" t="n">
-        <v>77553</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,38 +1132,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416207</v>
+        <v>416197</v>
       </c>
       <c r="R6" t="n">
-        <v>7039007</v>
+        <v>7038994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,13 +1207,9 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1221,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719884</v>
+        <v>121719888</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,39 +1242,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416043</v>
+        <v>416207</v>
       </c>
       <c r="R7" t="n">
-        <v>7039154</v>
+        <v>7039007</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1304,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1317,6 +1312,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719877</v>
+        <v>121719950</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>94614</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416081</v>
+        <v>416218</v>
       </c>
       <c r="R8" t="n">
-        <v>7039208</v>
+        <v>7038929</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,21 +1419,16 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719885</v>
+        <v>121719894</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416095</v>
+        <v>416218</v>
       </c>
       <c r="R10" t="n">
-        <v>7039081</v>
+        <v>7038922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719893</v>
+        <v>121719940</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>95361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,25 +1655,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416196</v>
+        <v>416053</v>
       </c>
       <c r="R11" t="n">
-        <v>7038951</v>
+        <v>7039233</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719941</v>
+        <v>121719890</v>
       </c>
       <c r="B12" t="n">
-        <v>82400</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416015</v>
+        <v>416194</v>
       </c>
       <c r="R12" t="n">
-        <v>7039205</v>
+        <v>7038973</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,12 +1815,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,26 +1831,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719938</v>
+        <v>121719933</v>
       </c>
       <c r="B13" t="n">
-        <v>95361</v>
+        <v>80284</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,25 +1864,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2420</v>
+        <v>738</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416137</v>
+        <v>416132</v>
       </c>
       <c r="R13" t="n">
-        <v>7039127</v>
+        <v>7039143</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719948</v>
+        <v>121719945</v>
       </c>
       <c r="B14" t="n">
-        <v>79601</v>
+        <v>74722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416217</v>
+        <v>416110</v>
       </c>
       <c r="R14" t="n">
-        <v>7038926</v>
+        <v>7039093</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719939</v>
+        <v>121719941</v>
       </c>
       <c r="B15" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416083</v>
+        <v>416015</v>
       </c>
       <c r="R15" t="n">
-        <v>7039207</v>
+        <v>7039205</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719894</v>
+        <v>121719942</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>79048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1778</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416218</v>
+        <v>416016</v>
       </c>
       <c r="R16" t="n">
-        <v>7038922</v>
+        <v>7039216</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,22 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719890</v>
+        <v>121719881</v>
       </c>
       <c r="B17" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416194</v>
+        <v>416016</v>
       </c>
       <c r="R17" t="n">
-        <v>7038973</v>
+        <v>7039217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>en</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719892</v>
+        <v>121719879</v>
       </c>
       <c r="B18" t="n">
-        <v>74722</v>
+        <v>79698</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416199</v>
+        <v>416015</v>
       </c>
       <c r="R18" t="n">
-        <v>7038968</v>
+        <v>7039216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2469,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719879</v>
+        <v>121719885</v>
       </c>
       <c r="B19" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416015</v>
+        <v>416095</v>
       </c>
       <c r="R19" t="n">
-        <v>7039216</v>
+        <v>7039081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,11 +2560,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719937</v>
+        <v>121719939</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416161</v>
+        <v>416083</v>
       </c>
       <c r="R20" t="n">
-        <v>7039079</v>
+        <v>7039207</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719950</v>
+        <v>121719948</v>
       </c>
       <c r="B21" t="n">
-        <v>94614</v>
+        <v>79601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416218</v>
+        <v>416217</v>
       </c>
       <c r="R21" t="n">
-        <v>7038929</v>
+        <v>7038926</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719881</v>
+        <v>121719878</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>79742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>229504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R22" t="n">
-        <v>7039217</v>
+        <v>7039209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2866,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2887,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719880</v>
+        <v>121719877</v>
       </c>
       <c r="B23" t="n">
         <v>79663</v>
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R23" t="n">
-        <v>7039217</v>
+        <v>7039208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2976,7 +2971,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719945</v>
+        <v>121719880</v>
       </c>
       <c r="B24" t="n">
-        <v>74722</v>
+        <v>79663</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,25 +3001,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,13 +3029,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416110</v>
+        <v>416016</v>
       </c>
       <c r="R24" t="n">
-        <v>7039093</v>
+        <v>7039217</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3064,12 +3059,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,26 +3075,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719882</v>
+        <v>121719892</v>
       </c>
       <c r="B25" t="n">
-        <v>74713</v>
+        <v>74722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,25 +3108,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416035</v>
+        <v>416199</v>
       </c>
       <c r="R25" t="n">
-        <v>7039188</v>
+        <v>7038968</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,11 +3182,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3203,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719878</v>
+        <v>121719937</v>
       </c>
       <c r="B26" t="n">
-        <v>79742</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229504</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,13 +3238,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416081</v>
+        <v>416161</v>
       </c>
       <c r="R26" t="n">
-        <v>7039209</v>
+        <v>7039079</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3273,12 +3268,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3293,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719942</v>
+        <v>121719882</v>
       </c>
       <c r="B28" t="n">
-        <v>79048</v>
+        <v>74713</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1778</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416016</v>
+        <v>416035</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7039188</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3477,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3498,16 +3493,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719938</v>
+        <v>121719884</v>
       </c>
       <c r="B3" t="n">
-        <v>95361</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2420</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416137</v>
+        <v>416043</v>
       </c>
       <c r="R3" t="n">
-        <v>7039127</v>
+        <v>7039154</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +879,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719893</v>
+        <v>121719938</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>95361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +928,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416196</v>
+        <v>416137</v>
       </c>
       <c r="R4" t="n">
-        <v>7038951</v>
+        <v>7039127</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719884</v>
+        <v>121719941</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,42 +1034,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416043</v>
+        <v>416015</v>
       </c>
       <c r="R5" t="n">
-        <v>7039154</v>
+        <v>7039205</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,17 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719889</v>
+        <v>121719879</v>
       </c>
       <c r="B6" t="n">
-        <v>79601</v>
+        <v>79698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,41 +1132,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416197</v>
+        <v>416015</v>
       </c>
       <c r="R6" t="n">
-        <v>7038994</v>
+        <v>7039216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,9 +1204,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1226,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719888</v>
+        <v>121719894</v>
       </c>
       <c r="B7" t="n">
-        <v>77553</v>
+        <v>79601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416207</v>
+        <v>416218</v>
       </c>
       <c r="R7" t="n">
-        <v>7039007</v>
+        <v>7038922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,11 +1313,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1333,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719950</v>
+        <v>121719888</v>
       </c>
       <c r="B8" t="n">
-        <v>94614</v>
+        <v>77553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1341,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416218</v>
+        <v>416207</v>
       </c>
       <c r="R8" t="n">
-        <v>7038929</v>
+        <v>7039007</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,26 +1415,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719887</v>
+        <v>121719939</v>
       </c>
       <c r="B9" t="n">
-        <v>80651</v>
+        <v>79698</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,40 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229558</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416179</v>
+        <v>416083</v>
       </c>
       <c r="R9" t="n">
-        <v>7039023</v>
+        <v>7039207</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,12 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,29 +1520,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719894</v>
+        <v>121719890</v>
       </c>
       <c r="B10" t="n">
-        <v>79601</v>
+        <v>79698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416218</v>
+        <v>416194</v>
       </c>
       <c r="R10" t="n">
-        <v>7038922</v>
+        <v>7038973</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1624,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1643,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719940</v>
+        <v>121719893</v>
       </c>
       <c r="B11" t="n">
-        <v>95361</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,25 +1657,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2420</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,13 +1685,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416053</v>
+        <v>416196</v>
       </c>
       <c r="R11" t="n">
-        <v>7039233</v>
+        <v>7038951</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,12 +1715,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,22 +1735,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719890</v>
+        <v>121719887</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>80651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,34 +1763,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>229558</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416194</v>
+        <v>416179</v>
       </c>
       <c r="R12" t="n">
-        <v>7038973</v>
+        <v>7039023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,13 +1834,9 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1852,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719933</v>
+        <v>121719942</v>
       </c>
       <c r="B13" t="n">
-        <v>80284</v>
+        <v>79048</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1869,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738</v>
+        <v>1778</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416132</v>
+        <v>416016</v>
       </c>
       <c r="R13" t="n">
-        <v>7039143</v>
+        <v>7039216</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1954,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719945</v>
+        <v>121719950</v>
       </c>
       <c r="B14" t="n">
-        <v>74722</v>
+        <v>94614</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416110</v>
+        <v>416218</v>
       </c>
       <c r="R14" t="n">
-        <v>7039093</v>
+        <v>7038929</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2056,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719941</v>
+        <v>121719880</v>
       </c>
       <c r="B15" t="n">
-        <v>82400</v>
+        <v>79663</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,13 +2097,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416015</v>
+        <v>416016</v>
       </c>
       <c r="R15" t="n">
-        <v>7039205</v>
+        <v>7039217</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,12 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,26 +2143,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719942</v>
+        <v>121719948</v>
       </c>
       <c r="B16" t="n">
-        <v>79048</v>
+        <v>79601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1778</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416016</v>
+        <v>416217</v>
       </c>
       <c r="R16" t="n">
-        <v>7039216</v>
+        <v>7038926</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2260,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719881</v>
+        <v>121719878</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>79742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,25 +2278,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>229504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R17" t="n">
-        <v>7039217</v>
+        <v>7039209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2352,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2367,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719879</v>
+        <v>121719882</v>
       </c>
       <c r="B18" t="n">
-        <v>79698</v>
+        <v>74713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2380,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416015</v>
+        <v>416035</v>
       </c>
       <c r="R18" t="n">
-        <v>7039216</v>
+        <v>7039188</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,7 +2457,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>död ved under kalkblock</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2474,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719885</v>
+        <v>121719881</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416095</v>
+        <v>416016</v>
       </c>
       <c r="R19" t="n">
-        <v>7039081</v>
+        <v>7039217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2576,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719939</v>
+        <v>121719889</v>
       </c>
       <c r="B20" t="n">
-        <v>79698</v>
+        <v>79601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,41 +2594,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416083</v>
+        <v>416197</v>
       </c>
       <c r="R20" t="n">
-        <v>7039207</v>
+        <v>7038994</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,12 +2655,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2660,28 +2669,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719948</v>
+        <v>121719877</v>
       </c>
       <c r="B21" t="n">
-        <v>79601</v>
+        <v>79663</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>229748</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,13 +2728,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416217</v>
+        <v>416081</v>
       </c>
       <c r="R21" t="n">
-        <v>7038926</v>
+        <v>7039208</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,12 +2758,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2764,26 +2774,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719878</v>
+        <v>121719892</v>
       </c>
       <c r="B22" t="n">
-        <v>79742</v>
+        <v>74722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229504</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416081</v>
+        <v>416199</v>
       </c>
       <c r="R22" t="n">
-        <v>7039209</v>
+        <v>7038968</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719877</v>
+        <v>121719891</v>
       </c>
       <c r="B23" t="n">
-        <v>79663</v>
+        <v>77553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,25 +2909,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416081</v>
+        <v>416194</v>
       </c>
       <c r="R23" t="n">
-        <v>7039208</v>
+        <v>7038972</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,7 +2986,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2989,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719880</v>
+        <v>121719885</v>
       </c>
       <c r="B24" t="n">
-        <v>79663</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3001,25 +3016,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3029,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416016</v>
+        <v>416095</v>
       </c>
       <c r="R24" t="n">
-        <v>7039217</v>
+        <v>7039081</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,11 +3090,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3096,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719892</v>
+        <v>121719933</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
+        <v>80284</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,25 +3118,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>738</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,13 +3146,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416199</v>
+        <v>416132</v>
       </c>
       <c r="R25" t="n">
-        <v>7038968</v>
+        <v>7039143</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3166,12 +3176,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3186,22 +3196,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719937</v>
+        <v>121719945</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416161</v>
+        <v>416110</v>
       </c>
       <c r="R26" t="n">
-        <v>7039079</v>
+        <v>7039093</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3300,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719891</v>
+        <v>121719937</v>
       </c>
       <c r="B27" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3316,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3340,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416194</v>
+        <v>416161</v>
       </c>
       <c r="R27" t="n">
-        <v>7038972</v>
+        <v>7039079</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3370,12 +3380,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,31 +3396,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719882</v>
+        <v>121719940</v>
       </c>
       <c r="B28" t="n">
-        <v>74713</v>
+        <v>95361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>2420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416035</v>
+        <v>416053</v>
       </c>
       <c r="R28" t="n">
-        <v>7039188</v>
+        <v>7039233</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3477,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3493,21 +3498,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719884</v>
+        <v>121719882</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,43 +816,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416043</v>
+        <v>416035</v>
       </c>
       <c r="R3" t="n">
-        <v>7039154</v>
+        <v>7039188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +882,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,6 +890,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719938</v>
+        <v>121719877</v>
       </c>
       <c r="B4" t="n">
-        <v>95361</v>
+        <v>79663</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2420</v>
+        <v>229748</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416137</v>
+        <v>416081</v>
       </c>
       <c r="R4" t="n">
-        <v>7039127</v>
+        <v>7039208</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,26 +997,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719941</v>
+        <v>121719939</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>79698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416015</v>
+        <v>416083</v>
       </c>
       <c r="R5" t="n">
-        <v>7039205</v>
+        <v>7039207</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719879</v>
+        <v>121719892</v>
       </c>
       <c r="B6" t="n">
-        <v>79698</v>
+        <v>74722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416015</v>
+        <v>416199</v>
       </c>
       <c r="R6" t="n">
-        <v>7039216</v>
+        <v>7038968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,11 +1206,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1227,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719894</v>
+        <v>121719888</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
+        <v>77553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,25 +1234,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416218</v>
+        <v>416207</v>
       </c>
       <c r="R7" t="n">
-        <v>7038922</v>
+        <v>7039007</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,6 +1308,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719888</v>
+        <v>121719879</v>
       </c>
       <c r="B8" t="n">
-        <v>77553</v>
+        <v>79698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416207</v>
+        <v>416015</v>
       </c>
       <c r="R8" t="n">
-        <v>7039007</v>
+        <v>7039216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719939</v>
+        <v>121719880</v>
       </c>
       <c r="B9" t="n">
-        <v>79698</v>
+        <v>79663</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,25 +1448,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416083</v>
+        <v>416016</v>
       </c>
       <c r="R9" t="n">
-        <v>7039207</v>
+        <v>7039217</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,26 +1522,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719890</v>
+        <v>121719941</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,13 +1583,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416194</v>
+        <v>416015</v>
       </c>
       <c r="R10" t="n">
-        <v>7038973</v>
+        <v>7039205</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,12 +1613,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,31 +1629,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719893</v>
+        <v>121719890</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416196</v>
+        <v>416194</v>
       </c>
       <c r="R11" t="n">
-        <v>7038951</v>
+        <v>7038973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,6 +1731,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1747,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719887</v>
+        <v>121719893</v>
       </c>
       <c r="B12" t="n">
-        <v>80651</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,37 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416179</v>
+        <v>416196</v>
       </c>
       <c r="R12" t="n">
-        <v>7039023</v>
+        <v>7038951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1836,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1853,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719942</v>
+        <v>121719878</v>
       </c>
       <c r="B13" t="n">
-        <v>79048</v>
+        <v>79742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,25 +1866,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1778</v>
+        <v>229504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,13 +1894,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R13" t="n">
-        <v>7039216</v>
+        <v>7039209</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,12 +1924,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,22 +1944,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719950</v>
+        <v>121719938</v>
       </c>
       <c r="B14" t="n">
-        <v>94614</v>
+        <v>95361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>2420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416218</v>
+        <v>416137</v>
       </c>
       <c r="R14" t="n">
-        <v>7038929</v>
+        <v>7039127</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2057,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719880</v>
+        <v>121719885</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416016</v>
+        <v>416095</v>
       </c>
       <c r="R15" t="n">
-        <v>7039217</v>
+        <v>7039081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,11 +2144,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2164,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719948</v>
+        <v>121719942</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>79048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1778</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416217</v>
+        <v>416016</v>
       </c>
       <c r="R16" t="n">
-        <v>7038926</v>
+        <v>7039216</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2266,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719878</v>
+        <v>121719940</v>
       </c>
       <c r="B17" t="n">
-        <v>79742</v>
+        <v>95361</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2274,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229504</v>
+        <v>2420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,13 +2302,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416081</v>
+        <v>416053</v>
       </c>
       <c r="R17" t="n">
-        <v>7039209</v>
+        <v>7039233</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2336,12 +2332,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,22 +2352,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719882</v>
+        <v>121719884</v>
       </c>
       <c r="B18" t="n">
-        <v>74713</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,38 +2376,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416035</v>
+        <v>416043</v>
       </c>
       <c r="R18" t="n">
-        <v>7039188</v>
+        <v>7039154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,6 +2447,11 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2454,11 +2460,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2475,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719881</v>
+        <v>121719891</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>77553</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2488,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2516,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416016</v>
+        <v>416194</v>
       </c>
       <c r="R19" t="n">
-        <v>7039217</v>
+        <v>7038972</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2565,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2582,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719889</v>
+        <v>121719933</v>
       </c>
       <c r="B20" t="n">
-        <v>79601</v>
+        <v>80284</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2594,44 +2595,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>738</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416197</v>
+        <v>416132</v>
       </c>
       <c r="R20" t="n">
-        <v>7038994</v>
+        <v>7039143</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,12 +2653,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2669,29 +2667,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719877</v>
+        <v>121719889</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>79601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,34 +2701,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229748</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416081</v>
+        <v>416197</v>
       </c>
       <c r="R21" t="n">
-        <v>7039208</v>
+        <v>7038994</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,13 +2772,9 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2795,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719892</v>
+        <v>121719881</v>
       </c>
       <c r="B22" t="n">
-        <v>74722</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2803,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416199</v>
+        <v>416016</v>
       </c>
       <c r="R22" t="n">
-        <v>7038968</v>
+        <v>7039217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2877,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2897,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719891</v>
+        <v>121719887</v>
       </c>
       <c r="B23" t="n">
-        <v>77553</v>
+        <v>80651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,34 +2914,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>229558</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416194</v>
+        <v>416179</v>
       </c>
       <c r="R23" t="n">
-        <v>7038972</v>
+        <v>7039023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,13 +2985,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3004,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719885</v>
+        <v>121719937</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3044,13 +3044,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416095</v>
+        <v>416161</v>
       </c>
       <c r="R24" t="n">
-        <v>7039081</v>
+        <v>7039079</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,22 +3094,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719933</v>
+        <v>121719950</v>
       </c>
       <c r="B25" t="n">
-        <v>80284</v>
+        <v>94614</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,25 +3118,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416132</v>
+        <v>416218</v>
       </c>
       <c r="R25" t="n">
-        <v>7039143</v>
+        <v>7038929</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719945</v>
+        <v>121719948</v>
       </c>
       <c r="B26" t="n">
-        <v>74722</v>
+        <v>79601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416110</v>
+        <v>416217</v>
       </c>
       <c r="R26" t="n">
-        <v>7039093</v>
+        <v>7038926</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719937</v>
+        <v>121719945</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416161</v>
+        <v>416110</v>
       </c>
       <c r="R27" t="n">
-        <v>7039079</v>
+        <v>7039093</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719940</v>
+        <v>121719894</v>
       </c>
       <c r="B28" t="n">
-        <v>95361</v>
+        <v>79601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2420</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416053</v>
+        <v>416218</v>
       </c>
       <c r="R28" t="n">
-        <v>7039233</v>
+        <v>7038922</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719878</v>
+        <v>121719938</v>
       </c>
       <c r="B13" t="n">
-        <v>79742</v>
+        <v>95361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,25 +1866,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229504</v>
+        <v>2420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416081</v>
+        <v>416137</v>
       </c>
       <c r="R13" t="n">
-        <v>7039209</v>
+        <v>7039127</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,22 +1944,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719938</v>
+        <v>121719878</v>
       </c>
       <c r="B14" t="n">
-        <v>95361</v>
+        <v>79742</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2420</v>
+        <v>229504</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416137</v>
+        <v>416081</v>
       </c>
       <c r="R14" t="n">
-        <v>7039127</v>
+        <v>7039209</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,12 +2046,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719884</v>
+        <v>121719891</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,39 +2380,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416043</v>
+        <v>416194</v>
       </c>
       <c r="R18" t="n">
-        <v>7039154</v>
+        <v>7038972</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,11 +2442,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2460,6 +2450,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719891</v>
+        <v>121719884</v>
       </c>
       <c r="B19" t="n">
-        <v>77553</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2492,34 +2487,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416194</v>
+        <v>416043</v>
       </c>
       <c r="R19" t="n">
-        <v>7038972</v>
+        <v>7039154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,6 +2554,11 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2562,11 +2567,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3512,6 +3512,108 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121974393</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79742</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>416238</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7038937</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719882</v>
+        <v>121719888</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>77553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416035</v>
+        <v>416207</v>
       </c>
       <c r="R3" t="n">
-        <v>7039188</v>
+        <v>7039007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>död ved under kalkblock</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719877</v>
+        <v>121719882</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229748</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416081</v>
+        <v>416035</v>
       </c>
       <c r="R4" t="n">
-        <v>7039208</v>
+        <v>7039188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>död ved under kalkblock</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719939</v>
+        <v>121719891</v>
       </c>
       <c r="B5" t="n">
-        <v>79698</v>
+        <v>77553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416083</v>
+        <v>416194</v>
       </c>
       <c r="R5" t="n">
-        <v>7039207</v>
+        <v>7038972</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,26 +1104,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719892</v>
+        <v>121719942</v>
       </c>
       <c r="B6" t="n">
-        <v>74722</v>
+        <v>79048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1778</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416199</v>
+        <v>416016</v>
       </c>
       <c r="R6" t="n">
-        <v>7038968</v>
+        <v>7039216</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,22 +1215,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719888</v>
+        <v>121719940</v>
       </c>
       <c r="B7" t="n">
-        <v>77553</v>
+        <v>95361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>2420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416207</v>
+        <v>416053</v>
       </c>
       <c r="R7" t="n">
-        <v>7039007</v>
+        <v>7039233</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,31 +1313,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719879</v>
+        <v>121719945</v>
       </c>
       <c r="B8" t="n">
-        <v>79698</v>
+        <v>74722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416015</v>
+        <v>416110</v>
       </c>
       <c r="R8" t="n">
-        <v>7039216</v>
+        <v>7039093</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,31 +1415,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719880</v>
+        <v>121719885</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,25 +1443,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416016</v>
+        <v>416095</v>
       </c>
       <c r="R9" t="n">
-        <v>7039217</v>
+        <v>7039081</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,11 +1517,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1543,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719941</v>
+        <v>121719893</v>
       </c>
       <c r="B10" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,13 +1573,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416015</v>
+        <v>416196</v>
       </c>
       <c r="R10" t="n">
-        <v>7039205</v>
+        <v>7038951</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,12 +1603,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,22 +1623,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719890</v>
+        <v>121719881</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,25 +1647,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416194</v>
+        <v>416016</v>
       </c>
       <c r="R11" t="n">
-        <v>7038973</v>
+        <v>7039217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1724,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>en</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1752,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719893</v>
+        <v>121719879</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,21 +1758,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416196</v>
+        <v>416015</v>
       </c>
       <c r="R12" t="n">
-        <v>7038951</v>
+        <v>7039216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,6 +1828,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719938</v>
+        <v>121719890</v>
       </c>
       <c r="B13" t="n">
-        <v>95361</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,25 +1861,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,13 +1889,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416137</v>
+        <v>416194</v>
       </c>
       <c r="R13" t="n">
-        <v>7039127</v>
+        <v>7038973</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,12 +1919,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,26 +1935,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719878</v>
+        <v>121719933</v>
       </c>
       <c r="B14" t="n">
-        <v>79742</v>
+        <v>80284</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229504</v>
+        <v>738</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416081</v>
+        <v>416132</v>
       </c>
       <c r="R14" t="n">
-        <v>7039209</v>
+        <v>7039143</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,22 +2046,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719885</v>
+        <v>121719948</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416095</v>
+        <v>416217</v>
       </c>
       <c r="R15" t="n">
-        <v>7039081</v>
+        <v>7038926</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,22 +2148,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719942</v>
+        <v>121719894</v>
       </c>
       <c r="B16" t="n">
-        <v>79048</v>
+        <v>79601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1778</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416016</v>
+        <v>416218</v>
       </c>
       <c r="R16" t="n">
-        <v>7039216</v>
+        <v>7038922</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,22 +2250,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719940</v>
+        <v>121719878</v>
       </c>
       <c r="B17" t="n">
-        <v>95361</v>
+        <v>79742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,25 +2274,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2420</v>
+        <v>229504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416053</v>
+        <v>416081</v>
       </c>
       <c r="R17" t="n">
-        <v>7039233</v>
+        <v>7039209</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,22 +2352,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719891</v>
+        <v>121719892</v>
       </c>
       <c r="B18" t="n">
-        <v>77553</v>
+        <v>74722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,21 +2380,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416194</v>
+        <v>416199</v>
       </c>
       <c r="R18" t="n">
-        <v>7038972</v>
+        <v>7038968</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,11 +2450,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2471,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719884</v>
+        <v>121719937</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,42 +2482,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416043</v>
+        <v>416161</v>
       </c>
       <c r="R19" t="n">
-        <v>7039154</v>
+        <v>7039079</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2546,17 +2536,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,22 +2556,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719933</v>
+        <v>121719880</v>
       </c>
       <c r="B20" t="n">
-        <v>80284</v>
+        <v>79663</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2580,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>738</v>
+        <v>229748</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,13 +2608,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416132</v>
+        <v>416016</v>
       </c>
       <c r="R20" t="n">
-        <v>7039143</v>
+        <v>7039217</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2653,12 +2638,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2669,26 +2654,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719889</v>
+        <v>121719950</v>
       </c>
       <c r="B21" t="n">
-        <v>79601</v>
+        <v>94614</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,40 +2691,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416197</v>
+        <v>416218</v>
       </c>
       <c r="R21" t="n">
-        <v>7038994</v>
+        <v>7038929</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2758,12 +2745,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,29 +2759,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719881</v>
+        <v>121719889</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>79601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,34 +2793,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416016</v>
+        <v>416197</v>
       </c>
       <c r="R22" t="n">
-        <v>7039217</v>
+        <v>7038994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,13 +2864,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2898,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719887</v>
+        <v>121719938</v>
       </c>
       <c r="B23" t="n">
-        <v>80651</v>
+        <v>95361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,44 +2895,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229558</v>
+        <v>2420</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416179</v>
+        <v>416137</v>
       </c>
       <c r="R23" t="n">
-        <v>7039023</v>
+        <v>7039127</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2971,12 +2953,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2985,29 +2967,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719937</v>
+        <v>121719941</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,21 +3001,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416161</v>
+        <v>416015</v>
       </c>
       <c r="R24" t="n">
-        <v>7039079</v>
+        <v>7039205</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3106,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719950</v>
+        <v>121719877</v>
       </c>
       <c r="B25" t="n">
-        <v>94614</v>
+        <v>79663</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,21 +3103,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>229748</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,13 +3127,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416218</v>
+        <v>416081</v>
       </c>
       <c r="R25" t="n">
-        <v>7038929</v>
+        <v>7039208</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,12 +3157,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3192,26 +3173,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719948</v>
+        <v>121719887</v>
       </c>
       <c r="B26" t="n">
-        <v>79601</v>
+        <v>80651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,41 +3206,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>229558</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416217</v>
+        <v>416179</v>
       </c>
       <c r="R26" t="n">
-        <v>7038926</v>
+        <v>7039023</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3278,12 +3267,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,28 +3281,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719945</v>
+        <v>121719884</v>
       </c>
       <c r="B27" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,37 +3316,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416110</v>
+        <v>416043</v>
       </c>
       <c r="R27" t="n">
-        <v>7039093</v>
+        <v>7039154</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3380,12 +3375,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3400,22 +3400,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719894</v>
+        <v>121719939</v>
       </c>
       <c r="B28" t="n">
-        <v>79601</v>
+        <v>79698</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416218</v>
+        <v>416083</v>
       </c>
       <c r="R28" t="n">
-        <v>7038922</v>
+        <v>7039207</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719888</v>
+        <v>121719894</v>
       </c>
       <c r="B3" t="n">
-        <v>77553</v>
+        <v>79614</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416207</v>
+        <v>416218</v>
       </c>
       <c r="R3" t="n">
-        <v>7039007</v>
+        <v>7038922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,11 +890,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -911,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719882</v>
+        <v>121719939</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>79711</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416035</v>
+        <v>416083</v>
       </c>
       <c r="R4" t="n">
-        <v>7039188</v>
+        <v>7039207</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,31 +992,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719891</v>
+        <v>121719940</v>
       </c>
       <c r="B5" t="n">
-        <v>77553</v>
+        <v>95379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>2420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416194</v>
+        <v>416053</v>
       </c>
       <c r="R5" t="n">
-        <v>7038972</v>
+        <v>7039233</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,31 +1094,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719942</v>
+        <v>121719945</v>
       </c>
       <c r="B6" t="n">
-        <v>79048</v>
+        <v>74735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1778</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416016</v>
+        <v>416110</v>
       </c>
       <c r="R6" t="n">
-        <v>7039216</v>
+        <v>7039093</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1227,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719940</v>
+        <v>121719889</v>
       </c>
       <c r="B7" t="n">
-        <v>95361</v>
+        <v>79614</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,37 +1228,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2420</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416053</v>
+        <v>416197</v>
       </c>
       <c r="R7" t="n">
-        <v>7039233</v>
+        <v>7038994</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,28 +1299,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719945</v>
+        <v>121719890</v>
       </c>
       <c r="B8" t="n">
-        <v>74722</v>
+        <v>79711</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,13 +1358,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416110</v>
+        <v>416194</v>
       </c>
       <c r="R8" t="n">
-        <v>7039093</v>
+        <v>7038973</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,26 +1404,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719885</v>
+        <v>121719892</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>74735</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416095</v>
+        <v>416199</v>
       </c>
       <c r="R9" t="n">
-        <v>7039081</v>
+        <v>7038968</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719893</v>
+        <v>121719881</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416196</v>
+        <v>416016</v>
       </c>
       <c r="R10" t="n">
-        <v>7038951</v>
+        <v>7039217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,6 +1613,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1635,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719881</v>
+        <v>121719888</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
+        <v>77566</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416016</v>
+        <v>416207</v>
       </c>
       <c r="R11" t="n">
-        <v>7039217</v>
+        <v>7039007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1723,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1742,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719879</v>
+        <v>121719877</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>79676</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416015</v>
+        <v>416081</v>
       </c>
       <c r="R12" t="n">
-        <v>7039216</v>
+        <v>7039208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1830,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1849,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719890</v>
+        <v>121719880</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>79676</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1860,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416194</v>
+        <v>416016</v>
       </c>
       <c r="R13" t="n">
-        <v>7038973</v>
+        <v>7039217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1937,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>en</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1956,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719933</v>
+        <v>121719882</v>
       </c>
       <c r="B14" t="n">
-        <v>80284</v>
+        <v>74726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>738</v>
+        <v>492</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,13 +1995,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416132</v>
+        <v>416035</v>
       </c>
       <c r="R14" t="n">
-        <v>7039143</v>
+        <v>7039188</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,12 +2025,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,16 +2041,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2061,7 +2065,7 @@
         <v>121719948</v>
       </c>
       <c r="B15" t="n">
-        <v>79601</v>
+        <v>79614</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719894</v>
+        <v>121719884</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>57365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,38 +2176,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416218</v>
+        <v>416043</v>
       </c>
       <c r="R16" t="n">
-        <v>7038922</v>
+        <v>7039154</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,6 +2245,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2262,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719878</v>
+        <v>121719941</v>
       </c>
       <c r="B17" t="n">
-        <v>79742</v>
+        <v>82414</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229504</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,13 +2316,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416081</v>
+        <v>416015</v>
       </c>
       <c r="R17" t="n">
-        <v>7039209</v>
+        <v>7039205</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,12 +2346,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,22 +2366,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719892</v>
+        <v>121719891</v>
       </c>
       <c r="B18" t="n">
-        <v>74722</v>
+        <v>77566</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416199</v>
+        <v>416194</v>
       </c>
       <c r="R18" t="n">
-        <v>7038968</v>
+        <v>7038972</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,6 +2464,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2466,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719937</v>
+        <v>121719887</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>80664</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,37 +2501,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416161</v>
+        <v>416179</v>
       </c>
       <c r="R19" t="n">
-        <v>7039079</v>
+        <v>7039023</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2536,12 +2558,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2550,28 +2572,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719880</v>
+        <v>121719933</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>80297</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,25 +2603,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229748</v>
+        <v>738</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2608,13 +2631,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416016</v>
+        <v>416132</v>
       </c>
       <c r="R20" t="n">
-        <v>7039217</v>
+        <v>7039143</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2638,12 +2661,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,31 +2677,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719950</v>
+        <v>121719893</v>
       </c>
       <c r="B21" t="n">
-        <v>94614</v>
+        <v>78629</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2687,25 +2705,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2667</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,13 +2733,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416218</v>
+        <v>416196</v>
       </c>
       <c r="R21" t="n">
-        <v>7038929</v>
+        <v>7038951</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2745,12 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,22 +2783,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719889</v>
+        <v>121719937</v>
       </c>
       <c r="B22" t="n">
-        <v>79601</v>
+        <v>78629</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2789,44 +2807,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416197</v>
+        <v>416161</v>
       </c>
       <c r="R22" t="n">
-        <v>7038994</v>
+        <v>7039079</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2850,12 +2865,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,29 +2879,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719938</v>
+        <v>121719950</v>
       </c>
       <c r="B23" t="n">
-        <v>95361</v>
+        <v>94632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2420</v>
+        <v>2667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416137</v>
+        <v>416218</v>
       </c>
       <c r="R23" t="n">
-        <v>7039127</v>
+        <v>7038929</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2985,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719941</v>
+        <v>121719879</v>
       </c>
       <c r="B24" t="n">
-        <v>82400</v>
+        <v>79711</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3001,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3028,10 +3042,10 @@
         <v>416015</v>
       </c>
       <c r="R24" t="n">
-        <v>7039205</v>
+        <v>7039216</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3055,12 +3069,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,26 +3085,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719877</v>
+        <v>121719885</v>
       </c>
       <c r="B25" t="n">
-        <v>79663</v>
+        <v>78629</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,25 +3118,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3127,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416081</v>
+        <v>416095</v>
       </c>
       <c r="R25" t="n">
-        <v>7039208</v>
+        <v>7039081</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,11 +3192,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3194,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719887</v>
+        <v>121719942</v>
       </c>
       <c r="B26" t="n">
-        <v>80651</v>
+        <v>79061</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,44 +3220,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229558</v>
+        <v>1778</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416179</v>
+        <v>416016</v>
       </c>
       <c r="R26" t="n">
-        <v>7039023</v>
+        <v>7039216</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,12 +3278,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,29 +3292,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719884</v>
+        <v>121719938</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>95379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,46 +3322,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416043</v>
+        <v>416137</v>
       </c>
       <c r="R27" t="n">
-        <v>7039154</v>
+        <v>7039127</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3375,17 +3380,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3400,22 +3400,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719939</v>
+        <v>121719878</v>
       </c>
       <c r="B28" t="n">
-        <v>79698</v>
+        <v>79755</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>229504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416083</v>
+        <v>416081</v>
       </c>
       <c r="R28" t="n">
-        <v>7039207</v>
+        <v>7039209</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79742</v>
+        <v>79755</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719894</v>
+        <v>121719884</v>
       </c>
       <c r="B3" t="n">
-        <v>79614</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,38 +816,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416218</v>
+        <v>416043</v>
       </c>
       <c r="R3" t="n">
-        <v>7038922</v>
+        <v>7039154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +885,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719939</v>
+        <v>121719933</v>
       </c>
       <c r="B4" t="n">
-        <v>79711</v>
+        <v>80299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +928,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416083</v>
+        <v>416132</v>
       </c>
       <c r="R4" t="n">
-        <v>7039207</v>
+        <v>7039143</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1008,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719940</v>
+        <v>121719878</v>
       </c>
       <c r="B5" t="n">
-        <v>95379</v>
+        <v>79757</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2420</v>
+        <v>229504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416053</v>
+        <v>416081</v>
       </c>
       <c r="R5" t="n">
-        <v>7039233</v>
+        <v>7039209</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,22 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719945</v>
+        <v>121719885</v>
       </c>
       <c r="B6" t="n">
-        <v>74735</v>
+        <v>78631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416110</v>
+        <v>416095</v>
       </c>
       <c r="R6" t="n">
-        <v>7039093</v>
+        <v>7039081</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,22 +1210,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719889</v>
+        <v>121719879</v>
       </c>
       <c r="B7" t="n">
-        <v>79614</v>
+        <v>79713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,41 +1234,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416197</v>
+        <v>416015</v>
       </c>
       <c r="R7" t="n">
-        <v>7038994</v>
+        <v>7039216</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,9 +1306,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1318,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719890</v>
+        <v>121719950</v>
       </c>
       <c r="B8" t="n">
-        <v>79711</v>
+        <v>94634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,25 +1341,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416194</v>
+        <v>416218</v>
       </c>
       <c r="R8" t="n">
-        <v>7038973</v>
+        <v>7038929</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,31 +1415,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719892</v>
+        <v>121719890</v>
       </c>
       <c r="B9" t="n">
-        <v>74735</v>
+        <v>79713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416199</v>
+        <v>416194</v>
       </c>
       <c r="R9" t="n">
-        <v>7038968</v>
+        <v>7038973</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,6 +1517,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1527,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719881</v>
+        <v>121719939</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,13 +1578,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416016</v>
+        <v>416083</v>
       </c>
       <c r="R10" t="n">
-        <v>7039217</v>
+        <v>7039207</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,31 +1624,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719888</v>
+        <v>121719892</v>
       </c>
       <c r="B11" t="n">
-        <v>77566</v>
+        <v>74737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1656,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416207</v>
+        <v>416199</v>
       </c>
       <c r="R11" t="n">
-        <v>7039007</v>
+        <v>7038968</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,11 +1726,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1741,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719877</v>
+        <v>121719945</v>
       </c>
       <c r="B12" t="n">
-        <v>79676</v>
+        <v>74737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1754,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416081</v>
+        <v>416110</v>
       </c>
       <c r="R12" t="n">
-        <v>7039208</v>
+        <v>7039093</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,12 +1812,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,31 +1828,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719880</v>
+        <v>121719942</v>
       </c>
       <c r="B13" t="n">
-        <v>79676</v>
+        <v>79063</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>1778</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1887,10 @@
         <v>416016</v>
       </c>
       <c r="R13" t="n">
-        <v>7039217</v>
+        <v>7039216</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1918,12 +1914,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,31 +1930,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719882</v>
+        <v>121719891</v>
       </c>
       <c r="B14" t="n">
-        <v>74726</v>
+        <v>77568</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1958,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416035</v>
+        <v>416194</v>
       </c>
       <c r="R14" t="n">
-        <v>7039188</v>
+        <v>7038972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2035,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>död ved under kalkblock</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2062,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719948</v>
+        <v>121719880</v>
       </c>
       <c r="B15" t="n">
-        <v>79614</v>
+        <v>79678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,13 +2093,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416217</v>
+        <v>416016</v>
       </c>
       <c r="R15" t="n">
-        <v>7038926</v>
+        <v>7039217</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,12 +2123,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,26 +2139,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719884</v>
+        <v>121719937</v>
       </c>
       <c r="B16" t="n">
-        <v>57365</v>
+        <v>78631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,42 +2176,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416043</v>
+        <v>416161</v>
       </c>
       <c r="R16" t="n">
-        <v>7039154</v>
+        <v>7039079</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2239,17 +2230,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,22 +2250,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719941</v>
+        <v>121719888</v>
       </c>
       <c r="B17" t="n">
-        <v>82414</v>
+        <v>77568</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,21 +2278,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2316,13 +2302,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416015</v>
+        <v>416207</v>
       </c>
       <c r="R17" t="n">
-        <v>7039205</v>
+        <v>7039007</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2346,12 +2332,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,26 +2348,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719891</v>
+        <v>121719881</v>
       </c>
       <c r="B18" t="n">
-        <v>77566</v>
+        <v>79741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2390,25 +2381,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416194</v>
+        <v>416016</v>
       </c>
       <c r="R18" t="n">
-        <v>7038972</v>
+        <v>7039217</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2458,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
+          <t>en</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2485,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719887</v>
+        <v>121719948</v>
       </c>
       <c r="B19" t="n">
-        <v>80664</v>
+        <v>79616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,44 +2488,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229558</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416179</v>
+        <v>416217</v>
       </c>
       <c r="R19" t="n">
-        <v>7039023</v>
+        <v>7038926</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2558,12 +2546,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2572,29 +2560,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719933</v>
+        <v>121719893</v>
       </c>
       <c r="B20" t="n">
-        <v>80297</v>
+        <v>78631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,25 +2590,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>738</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,13 +2618,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416132</v>
+        <v>416196</v>
       </c>
       <c r="R20" t="n">
-        <v>7039143</v>
+        <v>7038951</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2661,12 +2648,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2681,22 +2668,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719893</v>
+        <v>121719877</v>
       </c>
       <c r="B21" t="n">
-        <v>78629</v>
+        <v>79678</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,25 +2692,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416196</v>
+        <v>416081</v>
       </c>
       <c r="R21" t="n">
-        <v>7038951</v>
+        <v>7039208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,6 +2766,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2795,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719937</v>
+        <v>121719938</v>
       </c>
       <c r="B22" t="n">
-        <v>78629</v>
+        <v>95381</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416161</v>
+        <v>416137</v>
       </c>
       <c r="R22" t="n">
-        <v>7039079</v>
+        <v>7039127</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2897,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719950</v>
+        <v>121719894</v>
       </c>
       <c r="B23" t="n">
-        <v>94632</v>
+        <v>79616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2905,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2940,10 +2932,10 @@
         <v>416218</v>
       </c>
       <c r="R23" t="n">
-        <v>7038929</v>
+        <v>7038922</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2967,12 +2959,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2987,22 +2979,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719879</v>
+        <v>121719887</v>
       </c>
       <c r="B24" t="n">
-        <v>79711</v>
+        <v>80666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,34 +3007,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>229558</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416015</v>
+        <v>416179</v>
       </c>
       <c r="R24" t="n">
-        <v>7039216</v>
+        <v>7039023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,13 +3078,9 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3106,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719885</v>
+        <v>121719889</v>
       </c>
       <c r="B25" t="n">
-        <v>78629</v>
+        <v>79616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,38 +3109,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416095</v>
+        <v>416197</v>
       </c>
       <c r="R25" t="n">
-        <v>7039081</v>
+        <v>7038994</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,6 +3184,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3208,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719942</v>
+        <v>121719882</v>
       </c>
       <c r="B26" t="n">
-        <v>79061</v>
+        <v>74728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3224,21 +3219,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1778</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,13 +3243,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416016</v>
+        <v>416035</v>
       </c>
       <c r="R26" t="n">
-        <v>7039216</v>
+        <v>7039188</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3278,12 +3273,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,26 +3289,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719938</v>
+        <v>121719941</v>
       </c>
       <c r="B27" t="n">
-        <v>95379</v>
+        <v>82416</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3322,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2420</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416137</v>
+        <v>416015</v>
       </c>
       <c r="R27" t="n">
-        <v>7039127</v>
+        <v>7039205</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719878</v>
+        <v>121719940</v>
       </c>
       <c r="B28" t="n">
-        <v>79755</v>
+        <v>95381</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229504</v>
+        <v>2420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416081</v>
+        <v>416053</v>
       </c>
       <c r="R28" t="n">
-        <v>7039209</v>
+        <v>7039233</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79755</v>
+        <v>79757</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719884</v>
+        <v>121719877</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
+        <v>79679</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,43 +816,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416043</v>
+        <v>416081</v>
       </c>
       <c r="R3" t="n">
-        <v>7039154</v>
+        <v>7039208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +882,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,6 +890,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719933</v>
+        <v>121719940</v>
       </c>
       <c r="B4" t="n">
-        <v>80299</v>
+        <v>95388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,25 +923,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>738</v>
+        <v>2420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416132</v>
+        <v>416053</v>
       </c>
       <c r="R4" t="n">
-        <v>7039143</v>
+        <v>7039233</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1018,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719878</v>
+        <v>121719891</v>
       </c>
       <c r="B5" t="n">
-        <v>79757</v>
+        <v>77569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229504</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416081</v>
+        <v>416194</v>
       </c>
       <c r="R5" t="n">
-        <v>7039209</v>
+        <v>7038972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1099,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719885</v>
+        <v>121719948</v>
       </c>
       <c r="B6" t="n">
-        <v>78631</v>
+        <v>79617</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1132,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416095</v>
+        <v>416217</v>
       </c>
       <c r="R6" t="n">
-        <v>7039081</v>
+        <v>7038926</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,22 +1210,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719879</v>
+        <v>121719945</v>
       </c>
       <c r="B7" t="n">
-        <v>79713</v>
+        <v>74737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416015</v>
+        <v>416110</v>
       </c>
       <c r="R7" t="n">
-        <v>7039216</v>
+        <v>7039093</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,31 +1308,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719950</v>
+        <v>121719893</v>
       </c>
       <c r="B8" t="n">
-        <v>94634</v>
+        <v>78632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,25 +1336,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416218</v>
+        <v>416196</v>
       </c>
       <c r="R8" t="n">
-        <v>7038929</v>
+        <v>7038951</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,22 +1414,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719890</v>
+        <v>121719950</v>
       </c>
       <c r="B9" t="n">
-        <v>79713</v>
+        <v>94641</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,25 +1438,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,13 +1466,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416194</v>
+        <v>416218</v>
       </c>
       <c r="R9" t="n">
-        <v>7038973</v>
+        <v>7038929</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,12 +1496,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,31 +1512,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719939</v>
+        <v>121719892</v>
       </c>
       <c r="B10" t="n">
-        <v>79713</v>
+        <v>74737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,13 +1568,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416083</v>
+        <v>416199</v>
       </c>
       <c r="R10" t="n">
-        <v>7039207</v>
+        <v>7038968</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,12 +1598,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,22 +1618,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719892</v>
+        <v>121719881</v>
       </c>
       <c r="B11" t="n">
-        <v>74737</v>
+        <v>79742</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,25 +1642,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416199</v>
+        <v>416016</v>
       </c>
       <c r="R11" t="n">
-        <v>7038968</v>
+        <v>7039217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,6 +1716,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1742,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719945</v>
+        <v>121719941</v>
       </c>
       <c r="B12" t="n">
-        <v>74737</v>
+        <v>82417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416110</v>
+        <v>416015</v>
       </c>
       <c r="R12" t="n">
-        <v>7039093</v>
+        <v>7039205</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719942</v>
+        <v>121719889</v>
       </c>
       <c r="B13" t="n">
-        <v>79063</v>
+        <v>79617</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,41 +1851,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1778</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416016</v>
+        <v>416197</v>
       </c>
       <c r="R13" t="n">
-        <v>7039216</v>
+        <v>7038994</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1914,12 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,28 +1926,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719891</v>
+        <v>121719888</v>
       </c>
       <c r="B14" t="n">
-        <v>77568</v>
+        <v>77569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416194</v>
+        <v>416207</v>
       </c>
       <c r="R14" t="n">
-        <v>7038972</v>
+        <v>7039007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2055,7 @@
         <v>121719880</v>
       </c>
       <c r="B15" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719937</v>
+        <v>121719884</v>
       </c>
       <c r="B16" t="n">
-        <v>78631</v>
+        <v>57365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,37 +2175,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416161</v>
+        <v>416043</v>
       </c>
       <c r="R16" t="n">
-        <v>7039079</v>
+        <v>7039154</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2230,12 +2234,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,22 +2259,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719888</v>
+        <v>121719933</v>
       </c>
       <c r="B17" t="n">
-        <v>77568</v>
+        <v>80300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>738</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,13 +2311,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416207</v>
+        <v>416132</v>
       </c>
       <c r="R17" t="n">
-        <v>7039007</v>
+        <v>7039143</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,12 +2341,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,31 +2357,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719881</v>
+        <v>121719939</v>
       </c>
       <c r="B18" t="n">
-        <v>79741</v>
+        <v>79714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2409,13 +2413,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416016</v>
+        <v>416083</v>
       </c>
       <c r="R18" t="n">
-        <v>7039217</v>
+        <v>7039207</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2439,12 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,31 +2459,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719948</v>
+        <v>121719938</v>
       </c>
       <c r="B19" t="n">
-        <v>79616</v>
+        <v>95388</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2492,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>2420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2516,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416217</v>
+        <v>416137</v>
       </c>
       <c r="R19" t="n">
-        <v>7038926</v>
+        <v>7039127</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2578,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719893</v>
+        <v>121719885</v>
       </c>
       <c r="B20" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416196</v>
+        <v>416095</v>
       </c>
       <c r="R20" t="n">
-        <v>7038951</v>
+        <v>7039081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719877</v>
+        <v>121719894</v>
       </c>
       <c r="B21" t="n">
-        <v>79678</v>
+        <v>79617</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,21 +2695,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229748</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2720,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416081</v>
+        <v>416218</v>
       </c>
       <c r="R21" t="n">
-        <v>7039208</v>
+        <v>7038922</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2766,11 +2765,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2787,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719938</v>
+        <v>121719937</v>
       </c>
       <c r="B22" t="n">
-        <v>95381</v>
+        <v>78632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2793,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2420</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416137</v>
+        <v>416161</v>
       </c>
       <c r="R22" t="n">
-        <v>7039127</v>
+        <v>7039079</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2889,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719894</v>
+        <v>121719878</v>
       </c>
       <c r="B23" t="n">
-        <v>79616</v>
+        <v>79758</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,25 +2895,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>229504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416218</v>
+        <v>416081</v>
       </c>
       <c r="R23" t="n">
-        <v>7038922</v>
+        <v>7039209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,10 +2985,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719887</v>
+        <v>121719890</v>
       </c>
       <c r="B24" t="n">
-        <v>80666</v>
+        <v>79714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3007,37 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229558</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416179</v>
+        <v>416194</v>
       </c>
       <c r="R24" t="n">
-        <v>7039023</v>
+        <v>7038973</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,9 +3069,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3097,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719889</v>
+        <v>121719887</v>
       </c>
       <c r="B25" t="n">
-        <v>79616</v>
+        <v>80667</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,25 +3104,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>229558</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416197</v>
+        <v>416179</v>
       </c>
       <c r="R25" t="n">
-        <v>7038994</v>
+        <v>7039023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719882</v>
+        <v>121719942</v>
       </c>
       <c r="B26" t="n">
-        <v>74728</v>
+        <v>79064</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>1778</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,13 +3238,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416035</v>
+        <v>416016</v>
       </c>
       <c r="R26" t="n">
-        <v>7039188</v>
+        <v>7039216</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3273,12 +3268,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,31 +3284,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719941</v>
+        <v>121719882</v>
       </c>
       <c r="B27" t="n">
-        <v>82416</v>
+        <v>74728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3312,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3340,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416015</v>
+        <v>416035</v>
       </c>
       <c r="R27" t="n">
-        <v>7039205</v>
+        <v>7039188</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3380,12 +3370,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,26 +3386,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719940</v>
+        <v>121719879</v>
       </c>
       <c r="B28" t="n">
-        <v>95381</v>
+        <v>79714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,25 +3419,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416053</v>
+        <v>416015</v>
       </c>
       <c r="R28" t="n">
-        <v>7039233</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3477,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3498,16 +3493,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79757</v>
+        <v>79758</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719877</v>
+        <v>121719888</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>77576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416081</v>
+        <v>416207</v>
       </c>
       <c r="R3" t="n">
-        <v>7039208</v>
+        <v>7039007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719940</v>
+        <v>121719884</v>
       </c>
       <c r="B4" t="n">
-        <v>95388</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,41 +923,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2420</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416053</v>
+        <v>416043</v>
       </c>
       <c r="R4" t="n">
-        <v>7039233</v>
+        <v>7039154</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +986,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +1011,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719891</v>
+        <v>121719890</v>
       </c>
       <c r="B5" t="n">
-        <v>77569</v>
+        <v>79721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,7 +1066,7 @@
         <v>416194</v>
       </c>
       <c r="R5" t="n">
-        <v>7038972</v>
+        <v>7038973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1112,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1120,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719948</v>
+        <v>121719878</v>
       </c>
       <c r="B6" t="n">
-        <v>79617</v>
+        <v>79765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>229504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416217</v>
+        <v>416081</v>
       </c>
       <c r="R6" t="n">
-        <v>7038926</v>
+        <v>7039209</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1200,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719945</v>
+        <v>121719880</v>
       </c>
       <c r="B7" t="n">
-        <v>74737</v>
+        <v>79686</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416110</v>
+        <v>416016</v>
       </c>
       <c r="R7" t="n">
-        <v>7039093</v>
+        <v>7039217</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,12 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,26 +1318,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719893</v>
+        <v>121719948</v>
       </c>
       <c r="B8" t="n">
-        <v>78632</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,13 +1379,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416196</v>
+        <v>416217</v>
       </c>
       <c r="R8" t="n">
-        <v>7038951</v>
+        <v>7038926</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,12 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,22 +1429,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719950</v>
+        <v>121719885</v>
       </c>
       <c r="B9" t="n">
-        <v>94641</v>
+        <v>78639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1453,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416218</v>
+        <v>416095</v>
       </c>
       <c r="R9" t="n">
-        <v>7038929</v>
+        <v>7039081</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,12 +1511,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,22 +1531,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719892</v>
+        <v>121719933</v>
       </c>
       <c r="B10" t="n">
-        <v>74737</v>
+        <v>80307</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>738</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,13 +1583,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416199</v>
+        <v>416132</v>
       </c>
       <c r="R10" t="n">
-        <v>7038968</v>
+        <v>7039143</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,12 +1613,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,22 +1633,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719881</v>
+        <v>121719941</v>
       </c>
       <c r="B11" t="n">
-        <v>79742</v>
+        <v>82426</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,25 +1657,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,13 +1685,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416016</v>
+        <v>416015</v>
       </c>
       <c r="R11" t="n">
-        <v>7039217</v>
+        <v>7039205</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,12 +1715,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1716,31 +1731,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719941</v>
+        <v>121719879</v>
       </c>
       <c r="B12" t="n">
-        <v>82417</v>
+        <v>79721</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1790,10 @@
         <v>416015</v>
       </c>
       <c r="R12" t="n">
-        <v>7039205</v>
+        <v>7039216</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,12 +1817,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,26 +1833,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719889</v>
+        <v>121719891</v>
       </c>
       <c r="B13" t="n">
-        <v>79617</v>
+        <v>77576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,41 +1866,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416197</v>
+        <v>416194</v>
       </c>
       <c r="R13" t="n">
-        <v>7038994</v>
+        <v>7038972</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,9 +1938,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1945,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719888</v>
+        <v>121719945</v>
       </c>
       <c r="B14" t="n">
-        <v>77569</v>
+        <v>74741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1977,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416207</v>
+        <v>416110</v>
       </c>
       <c r="R14" t="n">
-        <v>7039007</v>
+        <v>7039093</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,31 +2047,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719880</v>
+        <v>121719893</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>78639</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416016</v>
+        <v>416196</v>
       </c>
       <c r="R15" t="n">
-        <v>7039217</v>
+        <v>7038951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,11 +2149,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2159,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719884</v>
+        <v>121719882</v>
       </c>
       <c r="B16" t="n">
-        <v>57365</v>
+        <v>74732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,43 +2177,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416043</v>
+        <v>416035</v>
       </c>
       <c r="R16" t="n">
-        <v>7039154</v>
+        <v>7039188</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,11 +2243,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2255,6 +2251,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2271,10 +2272,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719933</v>
+        <v>121719892</v>
       </c>
       <c r="B17" t="n">
-        <v>80300</v>
+        <v>74741</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2284,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>738</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416132</v>
+        <v>416199</v>
       </c>
       <c r="R17" t="n">
-        <v>7039143</v>
+        <v>7038968</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,12 +2342,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,22 +2362,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719939</v>
+        <v>121719889</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,41 +2386,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416083</v>
+        <v>416197</v>
       </c>
       <c r="R18" t="n">
-        <v>7039207</v>
+        <v>7038994</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,12 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,28 +2461,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719938</v>
+        <v>121719942</v>
       </c>
       <c r="B19" t="n">
-        <v>95388</v>
+        <v>79071</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2492,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2420</v>
+        <v>1778</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416137</v>
+        <v>416016</v>
       </c>
       <c r="R19" t="n">
-        <v>7039127</v>
+        <v>7039216</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2577,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719885</v>
+        <v>121719887</v>
       </c>
       <c r="B20" t="n">
-        <v>78632</v>
+        <v>80674</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,34 +2598,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416095</v>
+        <v>416179</v>
       </c>
       <c r="R20" t="n">
-        <v>7039081</v>
+        <v>7039023</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,6 +2669,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2679,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719894</v>
+        <v>121719881</v>
       </c>
       <c r="B21" t="n">
-        <v>79617</v>
+        <v>79749</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416218</v>
+        <v>416016</v>
       </c>
       <c r="R21" t="n">
-        <v>7038922</v>
+        <v>7039217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,6 +2774,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2784,7 +2798,7 @@
         <v>121719937</v>
       </c>
       <c r="B22" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2883,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719878</v>
+        <v>121719938</v>
       </c>
       <c r="B23" t="n">
-        <v>79758</v>
+        <v>95397</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,25 +2909,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229504</v>
+        <v>2420</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,13 +2937,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416081</v>
+        <v>416137</v>
       </c>
       <c r="R23" t="n">
-        <v>7039209</v>
+        <v>7039127</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2953,12 +2967,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2973,22 +2987,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719890</v>
+        <v>121719877</v>
       </c>
       <c r="B24" t="n">
-        <v>79714</v>
+        <v>79686</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,25 +3011,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3025,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416194</v>
+        <v>416081</v>
       </c>
       <c r="R24" t="n">
-        <v>7038973</v>
+        <v>7039208</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,7 +3088,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3092,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719887</v>
+        <v>121719950</v>
       </c>
       <c r="B25" t="n">
-        <v>80667</v>
+        <v>94650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3104,44 +3118,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229558</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416179</v>
+        <v>416218</v>
       </c>
       <c r="R25" t="n">
-        <v>7039023</v>
+        <v>7038929</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3165,12 +3176,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,29 +3190,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719942</v>
+        <v>121719894</v>
       </c>
       <c r="B26" t="n">
-        <v>79064</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,25 +3220,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1778</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,13 +3248,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416016</v>
+        <v>416218</v>
       </c>
       <c r="R26" t="n">
-        <v>7039216</v>
+        <v>7038922</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3268,12 +3278,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,22 +3298,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719882</v>
+        <v>121719939</v>
       </c>
       <c r="B27" t="n">
-        <v>74728</v>
+        <v>79721</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,25 +3322,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3340,13 +3350,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416035</v>
+        <v>416083</v>
       </c>
       <c r="R27" t="n">
-        <v>7039188</v>
+        <v>7039207</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3370,12 +3380,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,31 +3396,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719879</v>
+        <v>121719940</v>
       </c>
       <c r="B28" t="n">
-        <v>79714</v>
+        <v>95397</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3424,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>2420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3452,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416015</v>
+        <v>416053</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7039233</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3477,12 +3482,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3493,21 +3498,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79758</v>
+        <v>79765</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719888</v>
+        <v>121719884</v>
       </c>
       <c r="B3" t="n">
-        <v>77576</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,34 +820,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416207</v>
+        <v>416043</v>
       </c>
       <c r="R3" t="n">
-        <v>7039007</v>
+        <v>7039154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +887,11 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -890,11 +900,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -911,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719884</v>
+        <v>121719888</v>
       </c>
       <c r="B4" t="n">
-        <v>57369</v>
+        <v>77576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,39 +932,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416043</v>
+        <v>416207</v>
       </c>
       <c r="R4" t="n">
-        <v>7039154</v>
+        <v>7039007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,11 +994,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1007,6 +1002,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719878</v>
+        <v>121719948</v>
       </c>
       <c r="B6" t="n">
-        <v>79765</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229504</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416081</v>
+        <v>416217</v>
       </c>
       <c r="R6" t="n">
-        <v>7039209</v>
+        <v>7038926</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719880</v>
+        <v>121719878</v>
       </c>
       <c r="B7" t="n">
-        <v>79686</v>
+        <v>79765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>229504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416016</v>
+        <v>416081</v>
       </c>
       <c r="R7" t="n">
-        <v>7039217</v>
+        <v>7039209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,11 +1318,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1339,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719948</v>
+        <v>121719880</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>79686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>229748</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416217</v>
+        <v>416016</v>
       </c>
       <c r="R8" t="n">
-        <v>7038926</v>
+        <v>7039217</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,16 +1420,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719891</v>
+        <v>121719945</v>
       </c>
       <c r="B13" t="n">
-        <v>77576</v>
+        <v>74741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416194</v>
+        <v>416110</v>
       </c>
       <c r="R13" t="n">
-        <v>7038972</v>
+        <v>7039093</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,31 +1940,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719945</v>
+        <v>121719893</v>
       </c>
       <c r="B14" t="n">
-        <v>74741</v>
+        <v>78639</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,13 +1996,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416110</v>
+        <v>416196</v>
       </c>
       <c r="R14" t="n">
-        <v>7039093</v>
+        <v>7038951</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,12 +2026,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,22 +2046,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719893</v>
+        <v>121719891</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>77576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416196</v>
+        <v>416194</v>
       </c>
       <c r="R15" t="n">
-        <v>7038951</v>
+        <v>7038972</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,6 +2144,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719950</v>
+        <v>121719894</v>
       </c>
       <c r="B25" t="n">
-        <v>94650</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,21 +3122,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         <v>416218</v>
       </c>
       <c r="R25" t="n">
-        <v>7038929</v>
+        <v>7038922</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3196,22 +3196,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719894</v>
+        <v>121719939</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>79721</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416218</v>
+        <v>416083</v>
       </c>
       <c r="R26" t="n">
-        <v>7038922</v>
+        <v>7039207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,22 +3298,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719939</v>
+        <v>121719950</v>
       </c>
       <c r="B27" t="n">
-        <v>79721</v>
+        <v>94650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3322,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416083</v>
+        <v>416218</v>
       </c>
       <c r="R27" t="n">
-        <v>7039207</v>
+        <v>7038929</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3106,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719894</v>
+        <v>121719950</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>94650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,21 +3122,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         <v>416218</v>
       </c>
       <c r="R25" t="n">
-        <v>7038922</v>
+        <v>7038929</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3196,22 +3196,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719939</v>
+        <v>121719894</v>
       </c>
       <c r="B26" t="n">
-        <v>79721</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416083</v>
+        <v>416218</v>
       </c>
       <c r="R26" t="n">
-        <v>7039207</v>
+        <v>7038922</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,22 +3298,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719950</v>
+        <v>121719939</v>
       </c>
       <c r="B27" t="n">
-        <v>94650</v>
+        <v>79721</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3322,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416218</v>
+        <v>416083</v>
       </c>
       <c r="R27" t="n">
-        <v>7038929</v>
+        <v>7039207</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79765</v>
+        <v>79769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79769</v>
+        <v>79771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79771</v>
+        <v>79772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -3517,7 +3517,7 @@
         <v>121974393</v>
       </c>
       <c r="B29" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>281312</v>
+        <v>6746078</v>
       </c>
       <c r="B2" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>738</v>
+        <v>389</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,14 +708,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stavattsbergets NOtbrant, ca 350m S Nävermyrbäcken / Härrån går ihop., Jmt</t>
+          <t>Stavattsbergets NObrant,, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416161.3545631027</v>
+        <v>416169</v>
       </c>
       <c r="R2" t="n">
-        <v>7039114.283185869</v>
+        <v>7039106</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,24 +745,14 @@
           <t>2003-05-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-05-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ca 4,2 km Ö om Kalls kyrka,</t>
+          <t>ca 350 m S om sammanflödet Nävermyrbäcken / Härrån, ca 4,2 km O om Kalls kyrka,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +766,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>sluten skog, riklig på 10 m hög nordostexponerad lodyta av kalksten, 450 m.ö.h.</t>
+          <t>sluten skog, 100-årig granskog i nordostbrant, 450 m.ö.h.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ca 100-årig gran</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr"/>
@@ -804,55 +794,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121719884</v>
+        <v>121719882</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416043</v>
+        <v>416035</v>
       </c>
       <c r="R3" t="n">
-        <v>7039154</v>
+        <v>7039188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +867,6 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,6 +875,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>död ved under kalkblock</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,53 +896,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121719888</v>
+        <v>281312</v>
       </c>
       <c r="B4" t="n">
-        <v>77576</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stavattsberget, Jmt</t>
+          <t>Stavattsbergets NOtbrant, ca 350m S Nävermyrbäcken / Härrån går ihop., Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416207</v>
+        <v>416161</v>
       </c>
       <c r="R4" t="n">
-        <v>7039007</v>
+        <v>7039114</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2003-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2003-05-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 4,2 km Ö om Kalls kyrka,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,57 +985,57 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
-      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sluten skog, riklig på 10 m hög nordostexponerad lodyta av kalksten, 450 m.ö.h.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121719890</v>
+        <v>121719876</v>
       </c>
       <c r="B5" t="n">
-        <v>79721</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>738</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416194</v>
+        <v>416170</v>
       </c>
       <c r="R5" t="n">
-        <v>7038973</v>
+        <v>7039138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1094,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>lodyta kalksten</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1130,37 +1112,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121719948</v>
+        <v>121719933</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>738</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416217</v>
+        <v>416132</v>
       </c>
       <c r="R6" t="n">
-        <v>7038926</v>
+        <v>7039143</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1232,15 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121719878</v>
+        <v>6984878</v>
       </c>
       <c r="B7" t="n">
-        <v>79765</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229504</v>
+        <v>744</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Kalkbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Gymnocarpium robertianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hoffm.) Newman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416081</v>
+        <v>416090</v>
       </c>
       <c r="R7" t="n">
-        <v>7039209</v>
+        <v>7039212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,49 +1294,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121719880</v>
+        <v>121719941</v>
       </c>
       <c r="B8" t="n">
-        <v>79686</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416016</v>
+        <v>416015</v>
       </c>
       <c r="R8" t="n">
-        <v>7039217</v>
+        <v>7039205</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,12 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,58 +1387,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121719885</v>
+        <v>121719942</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416095</v>
+        <v>416016</v>
       </c>
       <c r="R9" t="n">
-        <v>7039081</v>
+        <v>7039216</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,65 +1488,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719933</v>
+        <v>6984890</v>
       </c>
       <c r="B10" t="n">
-        <v>80307</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>738</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416132</v>
+        <v>416113</v>
       </c>
       <c r="R10" t="n">
-        <v>7039143</v>
+        <v>7039203</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,12 +1567,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,31 +1583,36 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719941</v>
+        <v>121719879</v>
       </c>
       <c r="B11" t="n">
-        <v>82426</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1647,10 @@
         <v>416015</v>
       </c>
       <c r="R11" t="n">
-        <v>7039205</v>
+        <v>7039216</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,12 +1674,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,31 +1690,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719879</v>
+        <v>121719890</v>
       </c>
       <c r="B12" t="n">
-        <v>79721</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416015</v>
+        <v>416194</v>
       </c>
       <c r="R12" t="n">
-        <v>7039216</v>
+        <v>7038973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,15 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121719945</v>
+        <v>121719939</v>
       </c>
       <c r="B13" t="n">
-        <v>74741</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1824,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416110</v>
+        <v>416083</v>
       </c>
       <c r="R13" t="n">
-        <v>7039093</v>
+        <v>7039207</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1956,37 +1910,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121719893</v>
+        <v>121719938</v>
       </c>
       <c r="B14" t="n">
-        <v>78639</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,13 +1945,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416196</v>
+        <v>416137</v>
       </c>
       <c r="R14" t="n">
-        <v>7038951</v>
+        <v>7039127</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,12 +1975,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,49 +1995,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121719891</v>
+        <v>121719940</v>
       </c>
       <c r="B15" t="n">
-        <v>77576</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>2420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,13 +2042,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416194</v>
+        <v>416053</v>
       </c>
       <c r="R15" t="n">
-        <v>7038972</v>
+        <v>7039233</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,12 +2072,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,58 +2088,48 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>på barken på stammen av en gammal senvuxen gran</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121719882</v>
+        <v>6984884</v>
       </c>
       <c r="B16" t="n">
-        <v>74732</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>492</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2139,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416035</v>
+        <v>416173</v>
       </c>
       <c r="R16" t="n">
-        <v>7039188</v>
+        <v>7039119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,12 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2251,58 +2185,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>död ved under kalkblock</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121719892</v>
+        <v>7181543</v>
       </c>
       <c r="B17" t="n">
-        <v>74741</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2312,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416199</v>
+        <v>416144</v>
       </c>
       <c r="R17" t="n">
-        <v>7038968</v>
+        <v>7039156</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,27 +2286,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121719889</v>
+        <v>121719874</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,37 +2309,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416197</v>
+        <v>416171</v>
       </c>
       <c r="R18" t="n">
-        <v>7038994</v>
+        <v>7039137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,9 +2377,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>lodyta kalksten</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2480,37 +2400,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121719942</v>
+        <v>121719950</v>
       </c>
       <c r="B19" t="n">
-        <v>79071</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1778</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2435,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416016</v>
+        <v>416218</v>
       </c>
       <c r="R19" t="n">
-        <v>7039216</v>
+        <v>7038929</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2582,53 +2497,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121719887</v>
+        <v>121719875</v>
       </c>
       <c r="B20" t="n">
-        <v>80674</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229558</v>
+        <v>2779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416179</v>
+        <v>416170</v>
       </c>
       <c r="R20" t="n">
-        <v>7039023</v>
+        <v>7039138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,9 +2576,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>lodyta kalksten</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2688,37 +2599,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121719881</v>
+        <v>121719885</v>
       </c>
       <c r="B21" t="n">
-        <v>79749</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416016</v>
+        <v>416095</v>
       </c>
       <c r="R21" t="n">
-        <v>7039217</v>
+        <v>7039081</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2680,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2795,19 +2696,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121719937</v>
+        <v>121719893</v>
       </c>
       <c r="B22" t="n">
-        <v>78639</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2835,13 +2731,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416161</v>
+        <v>416196</v>
       </c>
       <c r="R22" t="n">
-        <v>7039079</v>
+        <v>7038951</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2865,12 +2761,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,49 +2781,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121719938</v>
+        <v>121719937</v>
       </c>
       <c r="B23" t="n">
-        <v>95397</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2420</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2828,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416137</v>
+        <v>416161</v>
       </c>
       <c r="R23" t="n">
-        <v>7039127</v>
+        <v>7039079</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2999,37 +2890,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121719877</v>
+        <v>121719892</v>
       </c>
       <c r="B24" t="n">
-        <v>79686</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416081</v>
+        <v>416199</v>
       </c>
       <c r="R24" t="n">
-        <v>7039208</v>
+        <v>7038968</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +2971,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3106,37 +2987,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121719950</v>
+        <v>121719945</v>
       </c>
       <c r="B25" t="n">
-        <v>94650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3022,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416218</v>
+        <v>416110</v>
       </c>
       <c r="R25" t="n">
-        <v>7038929</v>
+        <v>7039093</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3208,15 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121719894</v>
+        <v>121719889</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,16 +3113,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavattsberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416218</v>
+        <v>416197</v>
       </c>
       <c r="R26" t="n">
-        <v>7038922</v>
+        <v>7038994</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,6 +3166,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3310,37 +3185,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121719939</v>
+        <v>121719894</v>
       </c>
       <c r="B27" t="n">
-        <v>79721</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,13 +3220,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416083</v>
+        <v>416218</v>
       </c>
       <c r="R27" t="n">
-        <v>7039207</v>
+        <v>7038922</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3380,12 +3250,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3400,27 +3270,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121719940</v>
+        <v>121719948</v>
       </c>
       <c r="B28" t="n">
-        <v>95397</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3428,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2420</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416053</v>
+        <v>416217</v>
       </c>
       <c r="R28" t="n">
-        <v>7039233</v>
+        <v>7038926</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3514,37 +3379,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121974393</v>
+        <v>121719881</v>
       </c>
       <c r="B29" t="n">
-        <v>79777</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229504</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416238</v>
+        <v>416016</v>
       </c>
       <c r="R29" t="n">
-        <v>7038937</v>
+        <v>7039217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,12 +3444,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3600,6 +3460,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3613,6 +3478,913 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121719884</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>416043</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7039154</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121719888</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>416207</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7039007</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121719891</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>416194</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7038972</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>på barken på stammen av en gammal senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121719878</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>416081</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7039209</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121719934</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>416162</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7039132</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121974393</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>416238</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7038937</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121719887</v>
+      </c>
+      <c r="B36" t="n">
+        <v>81390</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229558</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Barkporlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pertusaria sommerfeltii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Flörke ex Sommerf.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>416179</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7039023</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121719877</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>416081</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7039208</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121719880</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stavattsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>416016</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7039217</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49534-2024 artfynd.xlsx
+++ b/artfynd/A 49534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6746078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719882</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/281312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719876</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719933</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6984878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719941</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719942</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6984890</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719879</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719890</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719939</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719938</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719940</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6984884</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2295,6 +2375,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7181543</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2397,6 +2482,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719874</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2494,6 +2584,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719950</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719875</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719885</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2790,6 +2895,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719893</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2887,6 +2997,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719937</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719892</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3081,6 +3201,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719945</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3182,6 +3307,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719889</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719894</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3376,6 +3511,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719948</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3478,6 +3618,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719881</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3585,6 +3730,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719884</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3687,6 +3837,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719888</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3789,6 +3944,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719891</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3886,6 +4046,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719878</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3983,6 +4148,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719934</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4080,6 +4250,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121974393</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4181,6 +4356,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719887</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4283,6 +4463,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719877</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4385,8 +4570,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121719880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>